--- a/source_data/Transaction_file20260406-062256.xlsx
+++ b/source_data/Transaction_file20260406-062256.xlsx
@@ -68,7 +68,7 @@
     <col min="3" max="3" width="8.296875" customWidth="true"/>
     <col min="4" max="4" width="13.734375" customWidth="true"/>
     <col min="5" max="5" width="11.5703125" customWidth="true"/>
-    <col min="6" max="6" width="7.56640625" customWidth="true"/>
+    <col min="6" max="6" width="7.6953125" customWidth="true"/>
     <col min="7" max="7" width="6.82421875" customWidth="true"/>
     <col min="8" max="8" width="17.484375" customWidth="true"/>
     <col min="9" max="9" width="9.01953125" customWidth="true"/>
@@ -86,9 +86,9 @@
     <col min="21" max="21" width="6.8828125" customWidth="true"/>
     <col min="22" max="22" width="17.1640625" customWidth="true"/>
     <col min="23" max="23" width="8.18359375" customWidth="true"/>
-    <col min="24" max="24" width="19.26953125" customWidth="true"/>
+    <col min="24" max="24" width="31.30078125" customWidth="true"/>
     <col min="25" max="25" width="20.921875" customWidth="true"/>
-    <col min="26" max="26" width="9.91015625" customWidth="true"/>
+    <col min="26" max="26" width="9.99609375" customWidth="true"/>
     <col min="27" max="27" width="3.95703125" customWidth="true"/>
     <col min="28" max="28" width="3.8984375" customWidth="true"/>
     <col min="29" max="29" width="16.0859375" customWidth="true"/>
@@ -120,7 +120,7 @@
     <col min="55" max="55" width="8.67578125" customWidth="true"/>
     <col min="56" max="56" width="11.7109375" customWidth="true"/>
     <col min="57" max="57" width="5.94140625" customWidth="true"/>
-    <col min="58" max="58" width="12.46875" customWidth="true"/>
+    <col min="58" max="58" width="12.49609375" customWidth="true"/>
     <col min="59" max="59" width="8.96875" customWidth="true"/>
     <col min="60" max="60" width="25.96875" customWidth="true"/>
     <col min="61" max="61" width="6.22265625" customWidth="true"/>
@@ -589,7 +589,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -629,17 +629,17 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t/>
+          <t>V****** K*****</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t/>
+          <t>83****9788</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t/>
+          <t>D**** T*********</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t/>
+          <t>62****4352</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t/>
+          <t>Y******** R**** G****</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t/>
+          <t>99****5552</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t/>
+          <t>M******* R**** G****</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t/>
+          <t>99****5552</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t/>
+          <t>D**** B******* S** S**</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t/>
+          <t>95****7535</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t/>
+          <t>D**** M**********</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t/>
+          <t>95****7535</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t/>
+          <t>D**** M**********</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t/>
+          <t>95****7535</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t/>
+          <t>D**** M**********</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t/>
+          <t>95****7535</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -3605,17 +3605,17 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t/>
+          <t>S** S***** P*******</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t/>
+          <t>73****2112</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -3977,17 +3977,17 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t/>
+          <t>B****** B*** S**** B*****</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t/>
+          <t>63****5193</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -4349,17 +4349,17 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t/>
+          <t>S***** S****</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t/>
+          <t>83****6856</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t/>
+          <t>M**** V****** S**</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t/>
+          <t>92****1340</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -5093,17 +5093,17 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t/>
+          <t>T***** D********</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t/>
+          <t>73****9208</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t/>
+          <t>T***** H*** C******</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t/>
+          <t>73****9208</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -5837,17 +5837,17 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t/>
+          <t>K******* E**** E****</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t/>
+          <t>98****0099</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -6209,17 +6209,17 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t/>
+          <t>K******* E**** E****</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t/>
+          <t>98****0099</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t/>
+          <t>R****** J******</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t/>
+          <t>77****0192</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -6953,17 +6953,17 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t/>
+          <t>R****** Y**** V****** R*****</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t/>
+          <t>77****0192</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t/>
+          <t>A***** N***</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t/>
+          <t>93****0583</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -7697,17 +7697,17 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t/>
+          <t>S****** J******</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t/>
+          <t>73****3690</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -8069,17 +8069,17 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t/>
+          <t>M***** S** C******</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t/>
+          <t>63****4637</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -8441,17 +8441,17 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t/>
+          <t>C******* A************* M*********</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t/>
+          <t>99****6244</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -8813,17 +8813,17 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t/>
+          <t>C******* A************* M*********</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t/>
+          <t>99****6244</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -9185,17 +9185,17 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t/>
+          <t>H******** R*****</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t/>
+          <t>63****8581</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -9557,17 +9557,17 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t/>
+          <t>H******** R*****</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t/>
+          <t>63****8581</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -9929,17 +9929,17 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t/>
+          <t>S**** Y****</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t/>
+          <t>81****6234</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t/>
+          <t>B**** A****** S***</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t/>
+          <t>90****9626</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -10673,17 +10673,17 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t/>
+          <t>V********* L*******</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t/>
+          <t>94****2946</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t/>
+          <t>V********* L*******</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -11417,17 +11417,17 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t/>
+          <t>K****** G**********</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t/>
+          <t>99****1635</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -11789,17 +11789,17 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t/>
+          <t>K****** H*****</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t/>
+          <t>99****1635</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -12161,17 +12161,17 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t/>
+          <t>K**** M*********</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t/>
+          <t>97****1309</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -12533,17 +12533,17 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t/>
+          <t>R****** V***********</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t/>
+          <t>98****9449</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -12905,17 +12905,17 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t/>
+          <t>R****** V***********</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t/>
+          <t>98****9449</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -13277,17 +13277,17 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t/>
+          <t>M******* Z*** K***</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t/>
+          <t>82****8795</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -13649,17 +13649,17 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t/>
+          <t>Y**** Y******* N****</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t/>
+          <t>94****1196</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -14021,17 +14021,17 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t/>
+          <t>M***** S******* L****** S** M** R**</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t/>
+          <t>80****0739</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -14393,17 +14393,17 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t/>
+          <t>S**** V****** S** V***** V******</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t/>
+          <t>85****3683</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -14765,17 +14765,17 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t/>
+          <t>P******** B******* S**</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t/>
+          <t>63****9629</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -15137,17 +15137,17 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t/>
+          <t>V******* L********</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t/>
+          <t>88****9151</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -15509,17 +15509,17 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t/>
+          <t>S**** A******</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t/>
+          <t>98****7290</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -15881,17 +15881,17 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t/>
+          <t>R***** H********* V*****</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t/>
+          <t>93****3084</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -16253,17 +16253,17 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t/>
+          <t>E******* M*******</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t/>
+          <t>96****1662</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -16585,7 +16585,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -16625,17 +16625,17 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t/>
+          <t>E******* M*******</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t/>
+          <t>96****1662</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -16997,17 +16997,17 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t/>
+          <t>S**** B******</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t/>
+          <t>79****8688</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -17369,17 +17369,17 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t/>
+          <t>S**** B********* S**</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t/>
+          <t>79****8688</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -17701,7 +17701,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -17741,17 +17741,17 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t/>
+          <t>V****** V******* M****</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t/>
+          <t>76****5088</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -18113,17 +18113,17 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t/>
+          <t>P******* C****** R******</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t/>
+          <t>90****9830</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -18445,7 +18445,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -18485,17 +18485,17 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t/>
+          <t>T**** T*** K****</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t/>
+          <t>97****8884</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -18857,17 +18857,17 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t/>
+          <t>T******* D** C******</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t/>
+          <t>90****6332</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -19189,7 +19189,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -19229,17 +19229,17 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t/>
+          <t>A****** A****** M*********</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t/>
+          <t>99****6244</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -19601,17 +19601,17 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t/>
+          <t>A****** A****** M*********</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t/>
+          <t>99****6244</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -19973,17 +19973,17 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t/>
+          <t>G******* J***** A***** A******</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t/>
+          <t>82****6967</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -20345,17 +20345,17 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t/>
+          <t>P******* J*******</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t/>
+          <t>95****0840</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -20677,7 +20677,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -20717,17 +20717,17 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t/>
+          <t>M****** P*****</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t/>
+          <t>99****3424</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -21089,17 +21089,17 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t/>
+          <t>B********** J** A******** S**** S*****</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t/>
+          <t>98****7129</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -21421,7 +21421,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -21461,17 +21461,17 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t/>
+          <t>B********** H*********</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t/>
+          <t>98****7129</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -21793,7 +21793,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -21833,17 +21833,17 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t/>
+          <t>G******* G**********</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t/>
+          <t>93****3464</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -22165,7 +22165,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -22205,17 +22205,17 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t/>
+          <t>G******* R***** N******</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t/>
+          <t>93****3464</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -22577,17 +22577,17 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t/>
+          <t>J**** C*****</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t/>
+          <t>81****3759</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t/>
+          <t>********6600</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -22949,17 +22949,17 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t/>
+          <t>S********** S*****</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t/>
+          <t>k*************@gmail.com</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t/>
+          <t>95****8421</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -29150,6 +29150,750 @@
         </is>
       </c>
       <c r="BV78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>11000357434273</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1775462904</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>13500.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>06-Apr-2026 13:38:37</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>NRNS</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>629926165014</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>M********** A**** L****</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>99****4686</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS FAILED</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE79" t="inlineStr">
+        <is>
+          <t>20008</t>
+        </is>
+      </c>
+      <c r="BF79" t="inlineStr">
+        <is>
+          <t>264999,266649</t>
+        </is>
+      </c>
+      <c r="BG79" t="inlineStr">
+        <is>
+          <t>2047,2055</t>
+        </is>
+      </c>
+      <c r="BH79" t="inlineStr">
+        <is>
+          <t>thirteen thousand five hundred</t>
+        </is>
+      </c>
+      <c r="BI79" t="inlineStr">
+        <is>
+          <t>17299</t>
+        </is>
+      </c>
+      <c r="BJ79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO79" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU79" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SALESIAN EDUCATION SOCIETY</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>753702</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>11000357637359</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1775543193</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>6750.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>07-Apr-2026 11:56:52</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>PREKGUKG</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>ICICI UPI QR</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>115726878456</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>********6600</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>SIBL0000899</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>08-Apr-2026 17:44:13</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>MERCHANT</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C****** V********</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>k*************@gmail.com</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>88****8971</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>6750.0</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>08-Apr-2026 17:44:13</t>
+        </is>
+      </c>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr">
+        <is>
+          <t>TRANSACTION IS SUCCESSFUL</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>KOTAK SALESIAN SCHOOL MANAGEMENT ACCOUNT</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="BE80" t="inlineStr">
+        <is>
+          <t>19901</t>
+        </is>
+      </c>
+      <c r="BF80" t="inlineStr">
+        <is>
+          <t>266636</t>
+        </is>
+      </c>
+      <c r="BG80" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="BH80" t="inlineStr">
+        <is>
+          <t>six thousand seven hundred fifty</t>
+        </is>
+      </c>
+      <c r="BI80" t="inlineStr">
+        <is>
+          <t>17187</t>
+        </is>
+      </c>
+      <c r="BJ80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BN80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BO80" t="inlineStr">
+        <is>
+          <t>UPI INTENT</t>
+        </is>
+      </c>
+      <c r="BP80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BQ80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BR80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BS80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BT80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU80" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BV80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
